--- a/excel/output_stats_vfvv/durbin/PerSubgraphStats.xlsx
+++ b/excel/output_stats_vfvv/durbin/PerSubgraphStats.xlsx
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
         <v>41</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
         <v>46</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
         <v>51</v>
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
         <v>43</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>7740440</v>
+        <v>7741440</v>
       </c>
       <c r="K9" t="n">
         <v>33665400</v>
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
         <v>63</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>750</v>
+        <v>1875</v>
       </c>
       <c r="K12" t="n">
         <v>3500</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>12</v>
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
         <v>23</v>
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K17" t="n">
         <v>73</v>
